--- a/docs/workbook-split/dateien/Umlagen.xlsx
+++ b/docs/workbook-split/dateien/Umlagen.xlsx
@@ -662,9 +662,8 @@
         <v>27266.67</v>
       </c>
       <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6">
-        <f>SUM(E7:F7)</f>
-        <v/>
+      <c r="G7" s="6" t="n">
+        <v>27266.67</v>
       </c>
       <c r="H7" s="1" t="n">
         <v>4</v>
@@ -692,9 +691,8 @@
         <v>16432.83</v>
       </c>
       <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6">
-        <f>SUM(E8:F8)</f>
-        <v/>
+      <c r="G8" s="6" t="n">
+        <v>16432.83</v>
       </c>
       <c r="H8" s="1" t="n">
         <v>1</v>
@@ -724,9 +722,8 @@
       <c r="F9" s="6" t="n">
         <v>-92864.49000000001</v>
       </c>
-      <c r="G9" s="6">
-        <f>SUM(E9:F9)</f>
-        <v/>
+      <c r="G9" s="6" t="n">
+        <v>-56158.01</v>
       </c>
       <c r="H9" s="1" t="n">
         <v>1</v>
@@ -756,9 +753,8 @@
       <c r="F10" s="6" t="n">
         <v>296941.99</v>
       </c>
-      <c r="G10" s="6">
-        <f>SUM(E10:F10)</f>
-        <v/>
+      <c r="G10" s="6" t="n">
+        <v>-5920.880000000005</v>
       </c>
       <c r="H10" s="1" t="n">
         <v>15</v>
@@ -786,9 +782,8 @@
         <v>45902.48</v>
       </c>
       <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6">
-        <f>SUM(E11:F11)</f>
-        <v/>
+      <c r="G11" s="6" t="n">
+        <v>45902.48</v>
       </c>
       <c r="H11" s="1" t="n">
         <v>5</v>
@@ -818,9 +813,8 @@
       <c r="F12" s="6" t="n">
         <v>3965</v>
       </c>
-      <c r="G12" s="6">
-        <f>SUM(E12:F12)</f>
-        <v/>
+      <c r="G12" s="6" t="n">
+        <v>19784.75</v>
       </c>
       <c r="H12" s="1" t="n">
         <v>2</v>
@@ -850,9 +844,8 @@
       <c r="F13" s="6" t="n">
         <v>-429383.95</v>
       </c>
-      <c r="G13" s="6">
-        <f>SUM(E13:F13)</f>
-        <v/>
+      <c r="G13" s="6" t="n">
+        <v>-334876.18</v>
       </c>
       <c r="H13" s="1" t="n">
         <v>1</v>
@@ -882,9 +875,8 @@
       <c r="F14" s="6" t="n">
         <v>955895.45</v>
       </c>
-      <c r="G14" s="6">
-        <f>SUM(E14:F14)</f>
-        <v/>
+      <c r="G14" s="6" t="n">
+        <v>-788786.77</v>
       </c>
       <c r="H14" s="1" t="n">
         <v>27</v>
@@ -912,9 +904,8 @@
         <v>22524.39</v>
       </c>
       <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6">
-        <f>SUM(E15:F15)</f>
-        <v/>
+      <c r="G15" s="6" t="n">
+        <v>22524.39</v>
       </c>
       <c r="H15" s="1" t="n">
         <v>3</v>
@@ -942,9 +933,8 @@
         <v>85442.86</v>
       </c>
       <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6">
-        <f>SUM(E16:F16)</f>
-        <v/>
+      <c r="G16" s="6" t="n">
+        <v>85442.86</v>
       </c>
       <c r="H16" s="1" t="n">
         <v>1</v>
@@ -974,9 +964,8 @@
       <c r="F17" s="6" t="n">
         <v>-404531.32</v>
       </c>
-      <c r="G17" s="6">
-        <f>SUM(E17:F17)</f>
-        <v/>
+      <c r="G17" s="6" t="n">
+        <v>-306023.29</v>
       </c>
       <c r="H17" s="1" t="n">
         <v>1</v>
@@ -1006,9 +995,8 @@
       <c r="F18" s="6" t="n">
         <v>854559.8199999999</v>
       </c>
-      <c r="G18" s="6">
-        <f>SUM(E18:F18)</f>
-        <v/>
+      <c r="G18" s="6" t="n">
+        <v>696182.61</v>
       </c>
       <c r="H18" s="1" t="n">
         <v>39</v>
@@ -1036,9 +1024,8 @@
         <v>33476.74</v>
       </c>
       <c r="F19" s="6" t="n"/>
-      <c r="G19" s="6">
-        <f>SUM(E19:F19)</f>
-        <v/>
+      <c r="G19" s="6" t="n">
+        <v>33476.74</v>
       </c>
       <c r="H19" s="1" t="n">
         <v>5</v>
@@ -1066,9 +1053,8 @@
         <v>147.77</v>
       </c>
       <c r="F20" s="6" t="n"/>
-      <c r="G20" s="6">
-        <f>SUM(E20:F20)</f>
-        <v/>
+      <c r="G20" s="6" t="n">
+        <v>147.77</v>
       </c>
       <c r="H20" s="1" t="n">
         <v>1</v>
@@ -1098,9 +1084,8 @@
       <c r="F21" s="6" t="n">
         <v>3278</v>
       </c>
-      <c r="G21" s="6">
-        <f>SUM(E21:F21)</f>
-        <v/>
+      <c r="G21" s="6" t="n">
+        <v>607991.85</v>
       </c>
       <c r="H21" s="1" t="n">
         <v>16</v>
@@ -1128,9 +1113,8 @@
         <v>14888.17</v>
       </c>
       <c r="F22" s="6" t="n"/>
-      <c r="G22" s="6">
-        <f>SUM(E22:F22)</f>
-        <v/>
+      <c r="G22" s="6" t="n">
+        <v>14888.17</v>
       </c>
       <c r="H22" s="1" t="n">
         <v>2</v>
@@ -1160,9 +1144,8 @@
       <c r="F23" s="6" t="n">
         <v>-588458.3100000001</v>
       </c>
-      <c r="G23" s="6">
-        <f>SUM(E23:F23)</f>
-        <v/>
+      <c r="G23" s="6" t="n">
+        <v>-491465.1200000001</v>
       </c>
       <c r="H23" s="1" t="n">
         <v>1</v>
@@ -1192,9 +1175,8 @@
       <c r="F24" s="6" t="n">
         <v>1232422.31</v>
       </c>
-      <c r="G24" s="6">
-        <f>SUM(E24:F24)</f>
-        <v/>
+      <c r="G24" s="6" t="n">
+        <v>-235319.8299999998</v>
       </c>
       <c r="H24" s="1" t="n">
         <v>40</v>
@@ -1222,9 +1204,8 @@
         <v>16506.24</v>
       </c>
       <c r="F25" s="6" t="n"/>
-      <c r="G25" s="6">
-        <f>SUM(E25:F25)</f>
-        <v/>
+      <c r="G25" s="6" t="n">
+        <v>16506.24</v>
       </c>
       <c r="H25" s="1" t="n">
         <v>1</v>
@@ -1381,9 +1362,8 @@
       <c r="H32" s="6" t="n">
         <v>-92864.49000000001</v>
       </c>
-      <c r="I32" s="6">
-        <f>SUM(G32:H32)</f>
-        <v/>
+      <c r="I32" s="6" t="n">
+        <v>-56158.01</v>
       </c>
       <c r="J32" s="1" t="n">
         <v>246</v>
@@ -1419,9 +1399,8 @@
         <v>14807.19</v>
       </c>
       <c r="H33" s="6" t="n"/>
-      <c r="I33" s="6">
-        <f>SUM(G33:H33)</f>
-        <v/>
+      <c r="I33" s="6" t="n">
+        <v>14807.19</v>
       </c>
       <c r="J33" s="1" t="n">
         <v>68</v>
@@ -1459,9 +1438,8 @@
       <c r="H34" s="6" t="n">
         <v>383640.92</v>
       </c>
-      <c r="I34" s="6">
-        <f>SUM(G34:H34)</f>
-        <v/>
+      <c r="I34" s="6" t="n">
+        <v>-68366.46000000002</v>
       </c>
       <c r="J34" s="1" t="n">
         <v>458</v>
@@ -1499,9 +1477,8 @@
       <c r="H35" s="6" t="n">
         <v>43140.39</v>
       </c>
-      <c r="I35" s="6">
-        <f>SUM(G35:H35)</f>
-        <v/>
+      <c r="I35" s="6" t="n">
+        <v>28180.94</v>
       </c>
       <c r="J35" s="1" t="n">
         <v>113</v>
@@ -1537,9 +1514,8 @@
         <v>16432.83</v>
       </c>
       <c r="H36" s="6" t="n"/>
-      <c r="I36" s="6">
-        <f>SUM(G36:H36)</f>
-        <v/>
+      <c r="I36" s="6" t="n">
+        <v>16432.83</v>
       </c>
       <c r="J36" s="1" t="n">
         <v>87</v>
@@ -1577,9 +1553,8 @@
       <c r="H37" s="6" t="n">
         <v>160.64</v>
       </c>
-      <c r="I37" s="6">
-        <f>SUM(G37:H37)</f>
-        <v/>
+      <c r="I37" s="6" t="n">
+        <v>1213.95</v>
       </c>
       <c r="J37" s="1" t="n">
         <v>13</v>
@@ -1617,9 +1592,8 @@
       <c r="H38" s="6" t="n">
         <v>515.39</v>
       </c>
-      <c r="I38" s="6">
-        <f>SUM(G38:H38)</f>
-        <v/>
+      <c r="I38" s="6" t="n">
+        <v>653.72</v>
       </c>
       <c r="J38" s="1" t="n">
         <v>20</v>
@@ -1655,9 +1629,8 @@
         <v>30</v>
       </c>
       <c r="H39" s="6" t="n"/>
-      <c r="I39" s="6">
-        <f>SUM(G39:H39)</f>
-        <v/>
+      <c r="I39" s="6" t="n">
+        <v>30</v>
       </c>
       <c r="J39" s="1" t="n">
         <v>10</v>
@@ -1693,9 +1666,8 @@
         <v>4781.24</v>
       </c>
       <c r="H40" s="6" t="n"/>
-      <c r="I40" s="6">
-        <f>SUM(G40:H40)</f>
-        <v/>
+      <c r="I40" s="6" t="n">
+        <v>4781.24</v>
       </c>
       <c r="J40" s="1" t="n">
         <v>46</v>
@@ -1731,9 +1703,8 @@
         <v>-5236.57</v>
       </c>
       <c r="H41" s="6" t="n"/>
-      <c r="I41" s="6">
-        <f>SUM(G41:H41)</f>
-        <v/>
+      <c r="I41" s="6" t="n">
+        <v>-5236.57</v>
       </c>
       <c r="J41" s="1" t="n">
         <v>2</v>
@@ -1769,9 +1740,8 @@
         <v>8664</v>
       </c>
       <c r="H42" s="6" t="n"/>
-      <c r="I42" s="6">
-        <f>SUM(G42:H42)</f>
-        <v/>
+      <c r="I42" s="6" t="n">
+        <v>8664</v>
       </c>
       <c r="J42" s="1" t="n">
         <v>10</v>
@@ -1807,9 +1777,8 @@
         <v>16506.24</v>
       </c>
       <c r="H43" s="6" t="n"/>
-      <c r="I43" s="6">
-        <f>SUM(G43:H43)</f>
-        <v/>
+      <c r="I43" s="6" t="n">
+        <v>16506.24</v>
       </c>
       <c r="J43" s="1" t="n">
         <v>105</v>
@@ -1847,9 +1816,8 @@
       <c r="H44" s="6" t="n">
         <v>41853.45</v>
       </c>
-      <c r="I44" s="6">
-        <f>SUM(G44:H44)</f>
-        <v/>
+      <c r="I44" s="6" t="n">
+        <v>36986.31</v>
       </c>
       <c r="J44" s="1" t="n">
         <v>38</v>
@@ -1887,9 +1855,8 @@
       <c r="H45" s="6" t="n">
         <v>-23.67</v>
       </c>
-      <c r="I45" s="6">
-        <f>SUM(G45:H45)</f>
-        <v/>
+      <c r="I45" s="6" t="n">
+        <v>-220.9</v>
       </c>
       <c r="J45" s="1" t="n">
         <v>5</v>
@@ -1927,9 +1894,8 @@
       <c r="H46" s="6" t="n">
         <v>281979.91</v>
       </c>
-      <c r="I46" s="6">
-        <f>SUM(G46:H46)</f>
-        <v/>
+      <c r="I46" s="6" t="n">
+        <v>732.25</v>
       </c>
       <c r="J46" s="1" t="n">
         <v>521</v>
@@ -1965,9 +1931,8 @@
         <v>147.77</v>
       </c>
       <c r="H47" s="6" t="n"/>
-      <c r="I47" s="6">
-        <f>SUM(G47:H47)</f>
-        <v/>
+      <c r="I47" s="6" t="n">
+        <v>147.77</v>
       </c>
       <c r="J47" s="1" t="n">
         <v>11</v>
@@ -2003,9 +1968,8 @@
         <v>10167.47</v>
       </c>
       <c r="H48" s="6" t="n"/>
-      <c r="I48" s="6">
-        <f>SUM(G48:H48)</f>
-        <v/>
+      <c r="I48" s="6" t="n">
+        <v>10167.47</v>
       </c>
       <c r="J48" s="1" t="n">
         <v>27</v>
@@ -2043,9 +2007,8 @@
       <c r="H49" s="6" t="n">
         <v>65194.65</v>
       </c>
-      <c r="I49" s="6">
-        <f>SUM(G49:H49)</f>
-        <v/>
+      <c r="I49" s="6" t="n">
+        <v>-15866.1</v>
       </c>
       <c r="J49" s="1" t="n">
         <v>183</v>
@@ -2081,9 +2044,8 @@
         <v>2570</v>
       </c>
       <c r="H50" s="6" t="n"/>
-      <c r="I50" s="6">
-        <f>SUM(G50:H50)</f>
-        <v/>
+      <c r="I50" s="6" t="n">
+        <v>2570</v>
       </c>
       <c r="J50" s="1" t="n">
         <v>9</v>
@@ -2121,9 +2083,8 @@
       <c r="H51" s="6" t="n">
         <v>211.05</v>
       </c>
-      <c r="I51" s="6">
-        <f>SUM(G51:H51)</f>
-        <v/>
+      <c r="I51" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="J51" s="1" t="n">
         <v>4</v>
@@ -2161,9 +2122,8 @@
       <c r="H52" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="I52" s="6">
-        <f>SUM(G52:H52)</f>
-        <v/>
+      <c r="I52" s="6" t="n">
+        <v>112</v>
       </c>
       <c r="J52" s="1" t="n">
         <v>2</v>
@@ -2201,9 +2161,8 @@
       <c r="H53" s="6" t="n">
         <v>356392.55</v>
       </c>
-      <c r="I53" s="6">
-        <f>SUM(G53:H53)</f>
-        <v/>
+      <c r="I53" s="6" t="n">
+        <v>-474435.49</v>
       </c>
       <c r="J53" s="1" t="n">
         <v>280</v>
@@ -2239,9 +2198,8 @@
         <v>0</v>
       </c>
       <c r="H54" s="6" t="n"/>
-      <c r="I54" s="6">
-        <f>SUM(G54:H54)</f>
-        <v/>
+      <c r="I54" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="J54" s="1" t="n">
         <v>2</v>
@@ -2277,9 +2235,8 @@
         <v>177.57</v>
       </c>
       <c r="H55" s="6" t="n"/>
-      <c r="I55" s="6">
-        <f>SUM(G55:H55)</f>
-        <v/>
+      <c r="I55" s="6" t="n">
+        <v>177.57</v>
       </c>
       <c r="J55" s="1" t="n">
         <v>2</v>
@@ -2317,9 +2274,8 @@
       <c r="H56" s="6" t="n">
         <v>-0.62</v>
       </c>
-      <c r="I56" s="6">
-        <f>SUM(G56:H56)</f>
-        <v/>
+      <c r="I56" s="6" t="n">
+        <v>-5.78</v>
       </c>
       <c r="J56" s="1" t="n">
         <v>4</v>
@@ -2357,9 +2313,8 @@
       <c r="H57" s="6" t="n">
         <v>8099.5</v>
       </c>
-      <c r="I57" s="6">
-        <f>SUM(G57:H57)</f>
-        <v/>
+      <c r="I57" s="6" t="n">
+        <v>12472.87</v>
       </c>
       <c r="J57" s="1" t="n">
         <v>32</v>
@@ -2397,9 +2352,8 @@
       <c r="H58" s="6" t="n">
         <v>-588458.3100000001</v>
       </c>
-      <c r="I58" s="6">
-        <f>SUM(G58:H58)</f>
-        <v/>
+      <c r="I58" s="6" t="n">
+        <v>-491465.1200000001</v>
       </c>
       <c r="J58" s="1" t="n">
         <v>643</v>
@@ -2435,9 +2389,8 @@
         <v>79.34</v>
       </c>
       <c r="H59" s="6" t="n"/>
-      <c r="I59" s="6">
-        <f>SUM(G59:H59)</f>
-        <v/>
+      <c r="I59" s="6" t="n">
+        <v>79.34</v>
       </c>
       <c r="J59" s="1" t="n">
         <v>2</v>
@@ -2475,9 +2428,8 @@
       <c r="H60" s="6" t="n">
         <v>65914</v>
       </c>
-      <c r="I60" s="6">
-        <f>SUM(G60:H60)</f>
-        <v/>
+      <c r="I60" s="6" t="n">
+        <v>150877.42</v>
       </c>
       <c r="J60" s="1" t="n">
         <v>190</v>
@@ -2513,9 +2465,8 @@
       <c r="H61" s="9" t="n">
         <v>7318.49</v>
       </c>
-      <c r="I61" s="9">
-        <f>SUM(G61:H61)</f>
-        <v/>
+      <c r="I61" s="9" t="n">
+        <v>-1470.33</v>
       </c>
       <c r="J61" s="8" t="n">
         <v>11</v>
@@ -2548,9 +2499,8 @@
       <c r="H62" s="9" t="n">
         <v>11809.3</v>
       </c>
-      <c r="I62" s="9">
-        <f>SUM(G62:H62)</f>
-        <v/>
+      <c r="I62" s="9" t="n">
+        <v>-23279.25</v>
       </c>
       <c r="J62" s="8" t="n">
         <v>33</v>
@@ -2581,9 +2531,8 @@
         <v>2488</v>
       </c>
       <c r="H63" s="9" t="n"/>
-      <c r="I63" s="9">
-        <f>SUM(G63:H63)</f>
-        <v/>
+      <c r="I63" s="9" t="n">
+        <v>2488</v>
       </c>
       <c r="J63" s="8" t="n">
         <v>6</v>
@@ -2616,9 +2565,8 @@
       <c r="H64" s="9" t="n">
         <v>309210.16</v>
       </c>
-      <c r="I64" s="9">
-        <f>SUM(G64:H64)</f>
-        <v/>
+      <c r="I64" s="9" t="n">
+        <v>289542.96</v>
       </c>
       <c r="J64" s="8" t="n">
         <v>301</v>
@@ -2651,9 +2599,8 @@
       <c r="H65" s="9" t="n">
         <v>345725.19</v>
       </c>
-      <c r="I65" s="9">
-        <f>SUM(G65:H65)</f>
-        <v/>
+      <c r="I65" s="9" t="n">
+        <v>461942.85</v>
       </c>
       <c r="J65" s="8" t="n">
         <v>588</v>
@@ -2684,9 +2631,8 @@
       <c r="H66" s="9" t="n">
         <v>828.8</v>
       </c>
-      <c r="I66" s="9">
-        <f>SUM(G66:H66)</f>
-        <v/>
+      <c r="I66" s="9" t="n">
+        <v>828.8</v>
       </c>
       <c r="J66" s="8" t="n">
         <v>3</v>
@@ -2719,9 +2665,8 @@
       <c r="H67" s="9" t="n">
         <v>10856.92</v>
       </c>
-      <c r="I67" s="9">
-        <f>SUM(G67:H67)</f>
-        <v/>
+      <c r="I67" s="9" t="n">
+        <v>-25245.17</v>
       </c>
       <c r="J67" s="8" t="n">
         <v>42</v>
@@ -2752,9 +2697,8 @@
         <v>-6059.53</v>
       </c>
       <c r="H68" s="9" t="n"/>
-      <c r="I68" s="9">
-        <f>SUM(G68:H68)</f>
-        <v/>
+      <c r="I68" s="9" t="n">
+        <v>-6059.53</v>
       </c>
       <c r="J68" s="8" t="n">
         <v>1</v>
@@ -2787,9 +2731,8 @@
       <c r="H69" s="9" t="n">
         <v>25006.67</v>
       </c>
-      <c r="I69" s="9">
-        <f>SUM(G69:H69)</f>
-        <v/>
+      <c r="I69" s="9" t="n">
+        <v>113346.86</v>
       </c>
       <c r="J69" s="8" t="n">
         <v>72</v>
@@ -2822,9 +2765,8 @@
       <c r="H70" s="9" t="n">
         <v>50.92</v>
       </c>
-      <c r="I70" s="9">
-        <f>SUM(G70:H70)</f>
-        <v/>
+      <c r="I70" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="J70" s="8" t="n">
         <v>3</v>
@@ -2857,9 +2799,8 @@
       <c r="H71" s="9" t="n">
         <v>2387.02</v>
       </c>
-      <c r="I71" s="9">
-        <f>SUM(G71:H71)</f>
-        <v/>
+      <c r="I71" s="9" t="n">
+        <v>-20146.24</v>
       </c>
       <c r="J71" s="8" t="n">
         <v>18</v>
@@ -2890,9 +2831,8 @@
         <v>4155.7</v>
       </c>
       <c r="H72" s="9" t="n"/>
-      <c r="I72" s="9">
-        <f>SUM(G72:H72)</f>
-        <v/>
+      <c r="I72" s="9" t="n">
+        <v>4155.7</v>
       </c>
       <c r="J72" s="8" t="n">
         <v>52</v>
@@ -2925,9 +2865,8 @@
       <c r="H73" s="9" t="n">
         <v>5796.21</v>
       </c>
-      <c r="I73" s="9">
-        <f>SUM(G73:H73)</f>
-        <v/>
+      <c r="I73" s="9" t="n">
+        <v>-2359.59</v>
       </c>
       <c r="J73" s="8" t="n">
         <v>23</v>
@@ -2960,9 +2899,8 @@
       <c r="H74" s="9" t="n">
         <v>3278</v>
       </c>
-      <c r="I74" s="9">
-        <f>SUM(G74:H74)</f>
-        <v/>
+      <c r="I74" s="9" t="n">
+        <v>3868.37</v>
       </c>
       <c r="J74" s="8" t="n">
         <v>23</v>
@@ -2995,9 +2933,8 @@
       <c r="H75" s="9" t="n">
         <v>7605.73</v>
       </c>
-      <c r="I75" s="9">
-        <f>SUM(G75:H75)</f>
-        <v/>
+      <c r="I75" s="9" t="n">
+        <v>30416.49</v>
       </c>
       <c r="J75" s="8" t="n">
         <v>43</v>
@@ -3028,9 +2965,8 @@
         <v>2702.81</v>
       </c>
       <c r="H76" s="9" t="n"/>
-      <c r="I76" s="9">
-        <f>SUM(G76:H76)</f>
-        <v/>
+      <c r="I76" s="9" t="n">
+        <v>2702.81</v>
       </c>
       <c r="J76" s="8" t="n">
         <v>28</v>
@@ -3061,9 +2997,8 @@
         <v>25780.46</v>
       </c>
       <c r="H77" s="9" t="n"/>
-      <c r="I77" s="9">
-        <f>SUM(G77:H77)</f>
-        <v/>
+      <c r="I77" s="9" t="n">
+        <v>25780.46</v>
       </c>
       <c r="J77" s="8" t="n">
         <v>1</v>
@@ -3094,9 +3029,8 @@
         <v>2847.73</v>
       </c>
       <c r="H78" s="9" t="n"/>
-      <c r="I78" s="9">
-        <f>SUM(G78:H78)</f>
-        <v/>
+      <c r="I78" s="9" t="n">
+        <v>2847.73</v>
       </c>
       <c r="J78" s="8" t="n">
         <v>1</v>
@@ -3127,9 +3061,8 @@
         <v>6739.56</v>
       </c>
       <c r="H79" s="9" t="n"/>
-      <c r="I79" s="9">
-        <f>SUM(G79:H79)</f>
-        <v/>
+      <c r="I79" s="9" t="n">
+        <v>6739.56</v>
       </c>
       <c r="J79" s="8" t="n">
         <v>51</v>
@@ -3162,9 +3095,8 @@
       <c r="H80" s="9" t="n">
         <v>396</v>
       </c>
-      <c r="I80" s="9">
-        <f>SUM(G80:H80)</f>
-        <v/>
+      <c r="I80" s="9" t="n">
+        <v>2588.04</v>
       </c>
       <c r="J80" s="8" t="n">
         <v>8</v>
@@ -3197,9 +3129,8 @@
       <c r="H81" s="9" t="n">
         <v>2637.75</v>
       </c>
-      <c r="I81" s="9">
-        <f>SUM(G81:H81)</f>
-        <v/>
+      <c r="I81" s="9" t="n">
+        <v>10607.62</v>
       </c>
       <c r="J81" s="8" t="n">
         <v>20</v>
@@ -3232,9 +3163,8 @@
       <c r="H82" s="9" t="n">
         <v>2056.89</v>
       </c>
-      <c r="I82" s="9">
-        <f>SUM(G82:H82)</f>
-        <v/>
+      <c r="I82" s="9" t="n">
+        <v>-10121.36</v>
       </c>
       <c r="J82" s="8" t="n">
         <v>10</v>
@@ -3265,9 +3195,8 @@
         <v>68245.31</v>
       </c>
       <c r="H83" s="9" t="n"/>
-      <c r="I83" s="9">
-        <f>SUM(G83:H83)</f>
-        <v/>
+      <c r="I83" s="9" t="n">
+        <v>68245.31</v>
       </c>
       <c r="J83" s="8" t="n">
         <v>122</v>
@@ -3298,9 +3227,8 @@
         <v>85442.86</v>
       </c>
       <c r="H84" s="9" t="n"/>
-      <c r="I84" s="9">
-        <f>SUM(G84:H84)</f>
-        <v/>
+      <c r="I84" s="9" t="n">
+        <v>85442.86</v>
       </c>
       <c r="J84" s="8" t="n">
         <v>180</v>
@@ -3331,9 +3259,8 @@
         <v>0</v>
       </c>
       <c r="H85" s="9" t="n"/>
-      <c r="I85" s="9">
-        <f>SUM(G85:H85)</f>
-        <v/>
+      <c r="I85" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="J85" s="8" t="n">
         <v>2</v>
@@ -3366,9 +3293,8 @@
       <c r="H86" s="9" t="n">
         <v>4076.14</v>
       </c>
-      <c r="I86" s="9">
-        <f>SUM(G86:H86)</f>
-        <v/>
+      <c r="I86" s="9" t="n">
+        <v>35338.26</v>
       </c>
       <c r="J86" s="8" t="n">
         <v>16</v>
@@ -3401,9 +3327,8 @@
       <c r="H87" s="9" t="n">
         <v>2077.62</v>
       </c>
-      <c r="I87" s="9">
-        <f>SUM(G87:H87)</f>
-        <v/>
+      <c r="I87" s="9" t="n">
+        <v>-2000.01</v>
       </c>
       <c r="J87" s="8" t="n">
         <v>10</v>
@@ -3434,9 +3359,8 @@
         <v>13406.42</v>
       </c>
       <c r="H88" s="9" t="n"/>
-      <c r="I88" s="9">
-        <f>SUM(G88:H88)</f>
-        <v/>
+      <c r="I88" s="9" t="n">
+        <v>13406.42</v>
       </c>
       <c r="J88" s="8" t="n">
         <v>46</v>
@@ -3469,9 +3393,8 @@
       <c r="H89" s="9" t="n">
         <v>-13.63</v>
       </c>
-      <c r="I89" s="9">
-        <f>SUM(G89:H89)</f>
-        <v/>
+      <c r="I89" s="9" t="n">
+        <v>-252.21</v>
       </c>
       <c r="J89" s="8" t="n">
         <v>31</v>
@@ -3504,9 +3427,8 @@
       <c r="H90" s="9" t="n">
         <v>21292.87</v>
       </c>
-      <c r="I90" s="9">
-        <f>SUM(G90:H90)</f>
-        <v/>
+      <c r="I90" s="9" t="n">
+        <v>24272.26</v>
       </c>
       <c r="J90" s="8" t="n">
         <v>42</v>
@@ -3539,9 +3461,8 @@
       <c r="H91" s="9" t="n">
         <v>1925.81</v>
       </c>
-      <c r="I91" s="9">
-        <f>SUM(G91:H91)</f>
-        <v/>
+      <c r="I91" s="9" t="n">
+        <v>-5132.1</v>
       </c>
       <c r="J91" s="8" t="n">
         <v>19</v>
@@ -3572,9 +3493,8 @@
         <v>456116.42</v>
       </c>
       <c r="H92" s="9" t="n"/>
-      <c r="I92" s="9">
-        <f>SUM(G92:H92)</f>
-        <v/>
+      <c r="I92" s="9" t="n">
+        <v>456116.42</v>
       </c>
       <c r="J92" s="8" t="n">
         <v>522</v>
@@ -3605,9 +3525,8 @@
         <v>8486.219999999999</v>
       </c>
       <c r="H93" s="9" t="n"/>
-      <c r="I93" s="9">
-        <f>SUM(G93:H93)</f>
-        <v/>
+      <c r="I93" s="9" t="n">
+        <v>8486.219999999999</v>
       </c>
       <c r="J93" s="8" t="n">
         <v>44</v>
@@ -3638,9 +3557,8 @@
         <v>12044.46</v>
       </c>
       <c r="H94" s="9" t="n"/>
-      <c r="I94" s="9">
-        <f>SUM(G94:H94)</f>
-        <v/>
+      <c r="I94" s="9" t="n">
+        <v>12044.46</v>
       </c>
       <c r="J94" s="8" t="n">
         <v>52</v>
@@ -3673,9 +3591,8 @@
       <c r="H95" s="9" t="n">
         <v>851.2</v>
       </c>
-      <c r="I95" s="9">
-        <f>SUM(G95:H95)</f>
-        <v/>
+      <c r="I95" s="9" t="n">
+        <v>-6418.64</v>
       </c>
       <c r="J95" s="8" t="n">
         <v>4</v>
@@ -3706,9 +3623,8 @@
         <v>9021.780000000001</v>
       </c>
       <c r="H96" s="9" t="n"/>
-      <c r="I96" s="9">
-        <f>SUM(G96:H96)</f>
-        <v/>
+      <c r="I96" s="9" t="n">
+        <v>9021.780000000001</v>
       </c>
       <c r="J96" s="8" t="n">
         <v>47</v>
@@ -3741,9 +3657,8 @@
       <c r="H97" s="9" t="n">
         <v>-429383.95</v>
       </c>
-      <c r="I97" s="9">
-        <f>SUM(G97:H97)</f>
-        <v/>
+      <c r="I97" s="9" t="n">
+        <v>-334876.18</v>
       </c>
       <c r="J97" s="8" t="n">
         <v>414</v>
@@ -3774,9 +3689,8 @@
         <v>761.1</v>
       </c>
       <c r="H98" s="9" t="n"/>
-      <c r="I98" s="9">
-        <f>SUM(G98:H98)</f>
-        <v/>
+      <c r="I98" s="9" t="n">
+        <v>761.1</v>
       </c>
       <c r="J98" s="8" t="n">
         <v>1</v>
@@ -3809,9 +3723,8 @@
       <c r="H99" s="9" t="n">
         <v>16733.74</v>
       </c>
-      <c r="I99" s="9">
-        <f>SUM(G99:H99)</f>
-        <v/>
+      <c r="I99" s="9" t="n">
+        <v>-16552.42</v>
       </c>
       <c r="J99" s="8" t="n">
         <v>40</v>
@@ -3842,9 +3755,8 @@
         <v>5683.12</v>
       </c>
       <c r="H100" s="9" t="n"/>
-      <c r="I100" s="9">
-        <f>SUM(G100:H100)</f>
-        <v/>
+      <c r="I100" s="9" t="n">
+        <v>5683.12</v>
       </c>
       <c r="J100" s="8" t="n">
         <v>2</v>
@@ -3875,9 +3787,8 @@
         <v>4243</v>
       </c>
       <c r="H101" s="9" t="n"/>
-      <c r="I101" s="9">
-        <f>SUM(G101:H101)</f>
-        <v/>
+      <c r="I101" s="9" t="n">
+        <v>4243</v>
       </c>
       <c r="J101" s="8" t="n">
         <v>31</v>
@@ -3910,9 +3821,8 @@
       <c r="H102" s="9" t="n">
         <v>5323</v>
       </c>
-      <c r="I102" s="9">
-        <f>SUM(G102:H102)</f>
-        <v/>
+      <c r="I102" s="9" t="n">
+        <v>-5031.42</v>
       </c>
       <c r="J102" s="8" t="n">
         <v>52</v>
@@ -3945,9 +3855,8 @@
       <c r="H103" s="9" t="n">
         <v>14700.53</v>
       </c>
-      <c r="I103" s="9">
-        <f>SUM(G103:H103)</f>
-        <v/>
+      <c r="I103" s="9" t="n">
+        <v>13411.52</v>
       </c>
       <c r="J103" s="8" t="n">
         <v>50</v>
@@ -3980,9 +3889,8 @@
       <c r="H104" s="9" t="n">
         <v>3672</v>
       </c>
-      <c r="I104" s="9">
-        <f>SUM(G104:H104)</f>
-        <v/>
+      <c r="I104" s="9" t="n">
+        <v>-11253.16</v>
       </c>
       <c r="J104" s="8" t="n">
         <v>17</v>
@@ -4013,9 +3921,8 @@
         <v>0</v>
       </c>
       <c r="H105" s="9" t="n"/>
-      <c r="I105" s="9">
-        <f>SUM(G105:H105)</f>
-        <v/>
+      <c r="I105" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="J105" s="8" t="n">
         <v>2</v>
@@ -4046,9 +3953,8 @@
         <v>-81006.27</v>
       </c>
       <c r="H106" s="9" t="n"/>
-      <c r="I106" s="9">
-        <f>SUM(G106:H106)</f>
-        <v/>
+      <c r="I106" s="9" t="n">
+        <v>-81006.27</v>
       </c>
       <c r="J106" s="8" t="n">
         <v>2</v>
@@ -4081,9 +3987,8 @@
       <c r="H107" s="9" t="n">
         <v>85122.32000000001</v>
       </c>
-      <c r="I107" s="9">
-        <f>SUM(G107:H107)</f>
-        <v/>
+      <c r="I107" s="9" t="n">
+        <v>-90919.59</v>
       </c>
       <c r="J107" s="8" t="n">
         <v>176</v>
@@ -4116,9 +4021,8 @@
       <c r="H108" s="9" t="n">
         <v>296221.88</v>
       </c>
-      <c r="I108" s="9">
-        <f>SUM(G108:H108)</f>
-        <v/>
+      <c r="I108" s="9" t="n">
+        <v>-179186.02</v>
       </c>
       <c r="J108" s="8" t="n">
         <v>249</v>
@@ -4151,9 +4055,8 @@
       <c r="H109" s="9" t="n">
         <v>5760.32</v>
       </c>
-      <c r="I109" s="9">
-        <f>SUM(G109:H109)</f>
-        <v/>
+      <c r="I109" s="9" t="n">
+        <v>-7561.860000000001</v>
       </c>
       <c r="J109" s="8" t="n">
         <v>36</v>
@@ -4186,9 +4089,8 @@
       <c r="H110" s="9" t="n">
         <v>117352.5</v>
       </c>
-      <c r="I110" s="9">
-        <f>SUM(G110:H110)</f>
-        <v/>
+      <c r="I110" s="9" t="n">
+        <v>243360.87</v>
       </c>
       <c r="J110" s="8" t="n">
         <v>116</v>
@@ -4221,9 +4123,8 @@
       <c r="H111" s="9" t="n">
         <v>1700.89</v>
       </c>
-      <c r="I111" s="9">
-        <f>SUM(G111:H111)</f>
-        <v/>
+      <c r="I111" s="9" t="n">
+        <v>-4915.349999999999</v>
       </c>
       <c r="J111" s="8" t="n">
         <v>7</v>
@@ -4254,9 +4155,8 @@
         <v>10449.93</v>
       </c>
       <c r="H112" s="9" t="n"/>
-      <c r="I112" s="9">
-        <f>SUM(G112:H112)</f>
-        <v/>
+      <c r="I112" s="9" t="n">
+        <v>10449.93</v>
       </c>
       <c r="J112" s="8" t="n">
         <v>35</v>
@@ -4289,9 +4189,8 @@
       <c r="H113" s="9" t="n">
         <v>92.2</v>
       </c>
-      <c r="I113" s="9">
-        <f>SUM(G113:H113)</f>
-        <v/>
+      <c r="I113" s="9" t="n">
+        <v>1176.84</v>
       </c>
       <c r="J113" s="8" t="n">
         <v>38</v>
@@ -4324,9 +4223,8 @@
       <c r="H114" s="9" t="n">
         <v>55734.37</v>
       </c>
-      <c r="I114" s="9">
-        <f>SUM(G114:H114)</f>
-        <v/>
+      <c r="I114" s="9" t="n">
+        <v>-116214.72</v>
       </c>
       <c r="J114" s="8" t="n">
         <v>135</v>
@@ -4357,9 +4255,8 @@
         <v>-37284</v>
       </c>
       <c r="H115" s="9" t="n"/>
-      <c r="I115" s="9">
-        <f>SUM(G115:H115)</f>
-        <v/>
+      <c r="I115" s="9" t="n">
+        <v>-37284</v>
       </c>
       <c r="J115" s="8" t="n">
         <v>1</v>
@@ -4392,9 +4289,8 @@
       <c r="H116" s="9" t="n">
         <v>70</v>
       </c>
-      <c r="I116" s="9">
-        <f>SUM(G116:H116)</f>
-        <v/>
+      <c r="I116" s="9" t="n">
+        <v>653.34</v>
       </c>
       <c r="J116" s="8" t="n">
         <v>5</v>
@@ -4425,9 +4321,8 @@
         <v>33.46</v>
       </c>
       <c r="H117" s="9" t="n"/>
-      <c r="I117" s="9">
-        <f>SUM(G117:H117)</f>
-        <v/>
+      <c r="I117" s="9" t="n">
+        <v>33.46</v>
       </c>
       <c r="J117" s="8" t="n">
         <v>2</v>
@@ -4458,9 +4353,8 @@
       <c r="H118" s="9" t="n">
         <v>69.59999999999999</v>
       </c>
-      <c r="I118" s="9">
-        <f>SUM(G118:H118)</f>
-        <v/>
+      <c r="I118" s="9" t="n">
+        <v>69.59999999999999</v>
       </c>
       <c r="J118" s="8" t="n">
         <v>1</v>
@@ -4491,9 +4385,8 @@
         <v>709.1799999999999</v>
       </c>
       <c r="H119" s="9" t="n"/>
-      <c r="I119" s="9">
-        <f>SUM(G119:H119)</f>
-        <v/>
+      <c r="I119" s="9" t="n">
+        <v>709.1799999999999</v>
       </c>
       <c r="J119" s="8" t="n">
         <v>17</v>
@@ -4526,9 +4419,8 @@
       <c r="H120" s="9" t="n">
         <v>-404531.32</v>
       </c>
-      <c r="I120" s="9">
-        <f>SUM(G120:H120)</f>
-        <v/>
+      <c r="I120" s="9" t="n">
+        <v>-306023.29</v>
       </c>
       <c r="J120" s="8" t="n">
         <v>521</v>
@@ -4561,9 +4453,8 @@
       <c r="H121" s="9" t="n">
         <v>748.16</v>
       </c>
-      <c r="I121" s="9">
-        <f>SUM(G121:H121)</f>
-        <v/>
+      <c r="I121" s="9" t="n">
+        <v>-7501.84</v>
       </c>
       <c r="J121" s="8" t="n">
         <v>5</v>
@@ -4596,9 +4487,8 @@
       <c r="H122" s="9" t="n">
         <v>1054.81</v>
       </c>
-      <c r="I122" s="9">
-        <f>SUM(G122:H122)</f>
-        <v/>
+      <c r="I122" s="9" t="n">
+        <v>4151.53</v>
       </c>
       <c r="J122" s="8" t="n">
         <v>13</v>
@@ -4629,9 +4519,8 @@
         <v>14.1</v>
       </c>
       <c r="H123" s="9" t="n"/>
-      <c r="I123" s="9">
-        <f>SUM(G123:H123)</f>
-        <v/>
+      <c r="I123" s="9" t="n">
+        <v>14.1</v>
       </c>
       <c r="J123" s="8" t="n">
         <v>1</v>
@@ -4662,9 +4551,8 @@
         <v>580</v>
       </c>
       <c r="H124" s="9" t="n"/>
-      <c r="I124" s="9">
-        <f>SUM(G124:H124)</f>
-        <v/>
+      <c r="I124" s="9" t="n">
+        <v>580</v>
       </c>
       <c r="J124" s="8" t="n">
         <v>1</v>
@@ -4697,9 +4585,8 @@
       <c r="H125" s="9" t="n">
         <v>82051.64</v>
       </c>
-      <c r="I125" s="9">
-        <f>SUM(G125:H125)</f>
-        <v/>
+      <c r="I125" s="9" t="n">
+        <v>-14968.43000000001</v>
       </c>
       <c r="J125" s="8" t="n">
         <v>63</v>
@@ -4732,9 +4619,8 @@
       <c r="H126" s="9" t="n">
         <v>1893.36</v>
       </c>
-      <c r="I126" s="9">
-        <f>SUM(G126:H126)</f>
-        <v/>
+      <c r="I126" s="9" t="n">
+        <v>-6739.23</v>
       </c>
       <c r="J126" s="8" t="n">
         <v>10</v>
@@ -4767,9 +4653,8 @@
       <c r="H127" s="9" t="n">
         <v>28368.92</v>
       </c>
-      <c r="I127" s="9">
-        <f>SUM(G127:H127)</f>
-        <v/>
+      <c r="I127" s="9" t="n">
+        <v>-113799.47</v>
       </c>
       <c r="J127" s="8" t="n">
         <v>50</v>
@@ -4802,9 +4687,8 @@
       <c r="H128" s="9" t="n">
         <v>1386.24</v>
       </c>
-      <c r="I128" s="9">
-        <f>SUM(G128:H128)</f>
-        <v/>
+      <c r="I128" s="9" t="n">
+        <v>6679.809999999999</v>
       </c>
       <c r="J128" s="8" t="n">
         <v>15</v>
@@ -4835,9 +4719,8 @@
         <v>4555.48</v>
       </c>
       <c r="H129" s="9" t="n"/>
-      <c r="I129" s="9">
-        <f>SUM(G129:H129)</f>
-        <v/>
+      <c r="I129" s="9" t="n">
+        <v>4555.48</v>
       </c>
       <c r="J129" s="8" t="n">
         <v>53</v>
@@ -4868,9 +4751,8 @@
         <v>10092.16</v>
       </c>
       <c r="H130" s="9" t="n"/>
-      <c r="I130" s="9">
-        <f>SUM(G130:H130)</f>
-        <v/>
+      <c r="I130" s="9" t="n">
+        <v>10092.16</v>
       </c>
       <c r="J130" s="8" t="n">
         <v>51</v>
@@ -4903,9 +4785,8 @@
       <c r="H131" s="9" t="n">
         <v>9045.49</v>
       </c>
-      <c r="I131" s="9">
-        <f>SUM(G131:H131)</f>
-        <v/>
+      <c r="I131" s="9" t="n">
+        <v>-7191.23</v>
       </c>
       <c r="J131" s="8" t="n">
         <v>36</v>
@@ -4938,9 +4819,8 @@
       <c r="H132" s="9" t="n">
         <v>3774.25</v>
       </c>
-      <c r="I132" s="9">
-        <f>SUM(G132:H132)</f>
-        <v/>
+      <c r="I132" s="9" t="n">
+        <v>-4108.72</v>
       </c>
       <c r="J132" s="8" t="n">
         <v>9</v>
@@ -4971,9 +4851,8 @@
         <v>0</v>
       </c>
       <c r="H133" s="9" t="n"/>
-      <c r="I133" s="9">
-        <f>SUM(G133:H133)</f>
-        <v/>
+      <c r="I133" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="J133" s="8" t="n">
         <v>2</v>
@@ -5006,9 +4885,8 @@
       <c r="H134" s="9" t="n">
         <v>-48.24</v>
       </c>
-      <c r="I134" s="9">
-        <f>SUM(G134:H134)</f>
-        <v/>
+      <c r="I134" s="9" t="n">
+        <v>39428.49000000001</v>
       </c>
       <c r="J134" s="8" t="n">
         <v>13</v>
@@ -5039,9 +4917,8 @@
         <v>1481.75</v>
       </c>
       <c r="H135" s="9" t="n"/>
-      <c r="I135" s="9">
-        <f>SUM(G135:H135)</f>
-        <v/>
+      <c r="I135" s="9" t="n">
+        <v>1481.75</v>
       </c>
       <c r="J135" s="8" t="n">
         <v>9</v>
@@ -5072,9 +4949,8 @@
         <v>6447.83</v>
       </c>
       <c r="H136" s="9" t="n"/>
-      <c r="I136" s="9">
-        <f>SUM(G136:H136)</f>
-        <v/>
+      <c r="I136" s="9" t="n">
+        <v>6447.83</v>
       </c>
       <c r="J136" s="8" t="n">
         <v>1</v>
@@ -5105,9 +4981,8 @@
         <v>1010</v>
       </c>
       <c r="H137" s="9" t="n"/>
-      <c r="I137" s="9">
-        <f>SUM(G137:H137)</f>
-        <v/>
+      <c r="I137" s="9" t="n">
+        <v>1010</v>
       </c>
       <c r="J137" s="8" t="n">
         <v>2</v>
@@ -5140,9 +5015,8 @@
       <c r="H138" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="I138" s="9">
-        <f>SUM(G138:H138)</f>
-        <v/>
+      <c r="I138" s="9" t="n">
+        <v>59789.16</v>
       </c>
       <c r="J138" s="8" t="n">
         <v>7</v>
@@ -5173,9 +5047,8 @@
         <v>7875</v>
       </c>
       <c r="H139" s="9" t="n"/>
-      <c r="I139" s="9">
-        <f>SUM(G139:H139)</f>
-        <v/>
+      <c r="I139" s="9" t="n">
+        <v>7875</v>
       </c>
       <c r="J139" s="8" t="n">
         <v>9</v>
@@ -5208,9 +5081,8 @@
       <c r="H140" s="9" t="n">
         <v>33.48</v>
       </c>
-      <c r="I140" s="9">
-        <f>SUM(G140:H140)</f>
-        <v/>
+      <c r="I140" s="9" t="n">
+        <v>904.3200000000001</v>
       </c>
       <c r="J140" s="8" t="n">
         <v>5</v>
@@ -5241,9 +5113,8 @@
         <v>0</v>
       </c>
       <c r="H141" s="9" t="n"/>
-      <c r="I141" s="9">
-        <f>SUM(G141:H141)</f>
-        <v/>
+      <c r="I141" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="J141" s="8" t="n">
         <v>2</v>
@@ -5274,9 +5145,8 @@
         <v>48751</v>
       </c>
       <c r="H142" s="9" t="n"/>
-      <c r="I142" s="9">
-        <f>SUM(G142:H142)</f>
-        <v/>
+      <c r="I142" s="9" t="n">
+        <v>48751</v>
       </c>
       <c r="J142" s="8" t="n">
         <v>11</v>
@@ -5309,9 +5179,8 @@
       <c r="H143" s="9" t="n">
         <v>10303.26</v>
       </c>
-      <c r="I143" s="9">
-        <f>SUM(G143:H143)</f>
-        <v/>
+      <c r="I143" s="9" t="n">
+        <v>-3303.369999999999</v>
       </c>
       <c r="J143" s="8" t="n">
         <v>16</v>
@@ -5342,9 +5211,8 @@
         <v>2396.61</v>
       </c>
       <c r="H144" s="9" t="n"/>
-      <c r="I144" s="9">
-        <f>SUM(G144:H144)</f>
-        <v/>
+      <c r="I144" s="9" t="n">
+        <v>2396.61</v>
       </c>
       <c r="J144" s="8" t="n">
         <v>11</v>
@@ -5375,9 +5243,8 @@
         <v>7</v>
       </c>
       <c r="H145" s="9" t="n"/>
-      <c r="I145" s="9">
-        <f>SUM(G145:H145)</f>
-        <v/>
+      <c r="I145" s="9" t="n">
+        <v>7</v>
       </c>
       <c r="J145" s="8" t="n">
         <v>2</v>
@@ -5408,9 +5275,8 @@
         <v>65.02</v>
       </c>
       <c r="H146" s="9" t="n"/>
-      <c r="I146" s="9">
-        <f>SUM(G146:H146)</f>
-        <v/>
+      <c r="I146" s="9" t="n">
+        <v>65.02</v>
       </c>
       <c r="J146" s="8" t="n">
         <v>1</v>
@@ -5441,9 +5307,8 @@
         <v>2162</v>
       </c>
       <c r="H147" s="9" t="n"/>
-      <c r="I147" s="9">
-        <f>SUM(G147:H147)</f>
-        <v/>
+      <c r="I147" s="9" t="n">
+        <v>2162</v>
       </c>
       <c r="J147" s="8" t="n">
         <v>2</v>
@@ -5476,9 +5341,8 @@
       <c r="H148" s="9" t="n">
         <v>83.51000000000001</v>
       </c>
-      <c r="I148" s="9">
-        <f>SUM(G148:H148)</f>
-        <v/>
+      <c r="I148" s="9" t="n">
+        <v>-312530</v>
       </c>
       <c r="J148" s="8" t="n">
         <v>32</v>
@@ -5509,9 +5373,8 @@
         <v>15364.19</v>
       </c>
       <c r="H149" s="9" t="n"/>
-      <c r="I149" s="9">
-        <f>SUM(G149:H149)</f>
-        <v/>
+      <c r="I149" s="9" t="n">
+        <v>15364.19</v>
       </c>
       <c r="J149" s="8" t="n">
         <v>61</v>
@@ -5544,9 +5407,8 @@
       <c r="H150" s="9" t="n">
         <v>15628.78</v>
       </c>
-      <c r="I150" s="9">
-        <f>SUM(G150:H150)</f>
-        <v/>
+      <c r="I150" s="9" t="n">
+        <v>-20389.28</v>
       </c>
       <c r="J150" s="8" t="n">
         <v>27</v>
@@ -5579,9 +5441,8 @@
       <c r="H151" s="9" t="n">
         <v>8445.530000000001</v>
       </c>
-      <c r="I151" s="9">
-        <f>SUM(G151:H151)</f>
-        <v/>
+      <c r="I151" s="9" t="n">
+        <v>-9741.33</v>
       </c>
       <c r="J151" s="8" t="n">
         <v>52</v>
@@ -5612,9 +5473,8 @@
         <v>7775.76</v>
       </c>
       <c r="H152" s="9" t="n"/>
-      <c r="I152" s="9">
-        <f>SUM(G152:H152)</f>
-        <v/>
+      <c r="I152" s="9" t="n">
+        <v>7775.76</v>
       </c>
       <c r="J152" s="8" t="n">
         <v>31</v>
@@ -5645,9 +5505,8 @@
         <v>10521.82</v>
       </c>
       <c r="H153" s="9" t="n"/>
-      <c r="I153" s="9">
-        <f>SUM(G153:H153)</f>
-        <v/>
+      <c r="I153" s="9" t="n">
+        <v>10521.82</v>
       </c>
       <c r="J153" s="8" t="n">
         <v>47</v>
@@ -5678,9 +5537,8 @@
         <v>15484.73</v>
       </c>
       <c r="H154" s="9" t="n"/>
-      <c r="I154" s="9">
-        <f>SUM(G154:H154)</f>
-        <v/>
+      <c r="I154" s="9" t="n">
+        <v>15484.73</v>
       </c>
       <c r="J154" s="8" t="n">
         <v>66</v>
@@ -5713,9 +5571,8 @@
       <c r="H155" s="9" t="n">
         <v>37906.39</v>
       </c>
-      <c r="I155" s="9">
-        <f>SUM(G155:H155)</f>
-        <v/>
+      <c r="I155" s="9" t="n">
+        <v>-137232.87</v>
       </c>
       <c r="J155" s="8" t="n">
         <v>51</v>
@@ -5746,9 +5603,8 @@
         <v>-63.3</v>
       </c>
       <c r="H156" s="9" t="n"/>
-      <c r="I156" s="9">
-        <f>SUM(G156:H156)</f>
-        <v/>
+      <c r="I156" s="9" t="n">
+        <v>-63.3</v>
       </c>
       <c r="J156" s="8" t="n">
         <v>8</v>
@@ -5779,9 +5635,8 @@
         <v>7178.67</v>
       </c>
       <c r="H157" s="9" t="n"/>
-      <c r="I157" s="9">
-        <f>SUM(G157:H157)</f>
-        <v/>
+      <c r="I157" s="9" t="n">
+        <v>7178.67</v>
       </c>
       <c r="J157" s="8" t="n">
         <v>35</v>
@@ -5814,9 +5669,8 @@
       <c r="H158" s="9" t="n">
         <v>-216.91</v>
       </c>
-      <c r="I158" s="9">
-        <f>SUM(G158:H158)</f>
-        <v/>
+      <c r="I158" s="9" t="n">
+        <v>-217.06</v>
       </c>
       <c r="J158" s="8" t="n">
         <v>4</v>
@@ -5847,9 +5701,8 @@
         <v>6459.33</v>
       </c>
       <c r="H159" s="9" t="n"/>
-      <c r="I159" s="9">
-        <f>SUM(G159:H159)</f>
-        <v/>
+      <c r="I159" s="9" t="n">
+        <v>6459.33</v>
       </c>
       <c r="J159" s="8" t="n">
         <v>100</v>
@@ -5882,9 +5735,8 @@
       <c r="H160" s="9" t="n">
         <v>62845.63</v>
       </c>
-      <c r="I160" s="9">
-        <f>SUM(G160:H160)</f>
-        <v/>
+      <c r="I160" s="9" t="n">
+        <v>94135.92</v>
       </c>
       <c r="J160" s="8" t="n">
         <v>61</v>
@@ -5915,9 +5767,8 @@
         <v>1800.95</v>
       </c>
       <c r="H161" s="9" t="n"/>
-      <c r="I161" s="9">
-        <f>SUM(G161:H161)</f>
-        <v/>
+      <c r="I161" s="9" t="n">
+        <v>1800.95</v>
       </c>
       <c r="J161" s="8" t="n">
         <v>4</v>
@@ -5948,9 +5799,8 @@
         <v>349.4</v>
       </c>
       <c r="H162" s="9" t="n"/>
-      <c r="I162" s="9">
-        <f>SUM(G162:H162)</f>
-        <v/>
+      <c r="I162" s="9" t="n">
+        <v>349.4</v>
       </c>
       <c r="J162" s="8" t="n">
         <v>1</v>
@@ -5983,9 +5833,8 @@
       <c r="H163" s="9" t="n">
         <v>3110.61</v>
       </c>
-      <c r="I163" s="9">
-        <f>SUM(G163:H163)</f>
-        <v/>
+      <c r="I163" s="9" t="n">
+        <v>-13975.9</v>
       </c>
       <c r="J163" s="8" t="n">
         <v>16</v>
@@ -6018,9 +5867,8 @@
       <c r="H164" s="9" t="n">
         <v>122323.84</v>
       </c>
-      <c r="I164" s="9">
-        <f>SUM(G164:H164)</f>
-        <v/>
+      <c r="I164" s="9" t="n">
+        <v>94430.2</v>
       </c>
       <c r="J164" s="8" t="n">
         <v>250</v>
@@ -6051,9 +5899,8 @@
         <v>-45582.42</v>
       </c>
       <c r="H165" s="9" t="n"/>
-      <c r="I165" s="9">
-        <f>SUM(G165:H165)</f>
-        <v/>
+      <c r="I165" s="9" t="n">
+        <v>-45582.42</v>
       </c>
       <c r="J165" s="8" t="n">
         <v>1</v>
@@ -6084,9 +5931,8 @@
         <v>799.38</v>
       </c>
       <c r="H166" s="9" t="n"/>
-      <c r="I166" s="9">
-        <f>SUM(G166:H166)</f>
-        <v/>
+      <c r="I166" s="9" t="n">
+        <v>799.38</v>
       </c>
       <c r="J166" s="8" t="n">
         <v>7</v>
@@ -6119,9 +5965,8 @@
       <c r="H167" s="9" t="n">
         <v>2159.46</v>
       </c>
-      <c r="I167" s="9">
-        <f>SUM(G167:H167)</f>
-        <v/>
+      <c r="I167" s="9" t="n">
+        <v>28895.07</v>
       </c>
       <c r="J167" s="8" t="n">
         <v>9</v>
@@ -6152,9 +5997,8 @@
         <v>0</v>
       </c>
       <c r="H168" s="9" t="n"/>
-      <c r="I168" s="9">
-        <f>SUM(G168:H168)</f>
-        <v/>
+      <c r="I168" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="J168" s="8" t="n">
         <v>2</v>
@@ -6187,9 +6031,8 @@
       <c r="H169" s="9" t="n">
         <v>41966.07</v>
       </c>
-      <c r="I169" s="9">
-        <f>SUM(G169:H169)</f>
-        <v/>
+      <c r="I169" s="9" t="n">
+        <v>-49841.05</v>
       </c>
       <c r="J169" s="8" t="n">
         <v>63</v>
@@ -6220,9 +6063,8 @@
       <c r="H170" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I170" s="9">
-        <f>SUM(G170:H170)</f>
-        <v/>
+      <c r="I170" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="J170" s="8" t="n">
         <v>2</v>
@@ -6255,9 +6097,8 @@
       <c r="H171" s="9" t="n">
         <v>2119.47</v>
       </c>
-      <c r="I171" s="9">
-        <f>SUM(G171:H171)</f>
-        <v/>
+      <c r="I171" s="9" t="n">
+        <v>-5658.530000000001</v>
       </c>
       <c r="J171" s="8" t="n">
         <v>14</v>
@@ -6288,9 +6129,8 @@
         <v>4285.08</v>
       </c>
       <c r="H172" s="9" t="n"/>
-      <c r="I172" s="9">
-        <f>SUM(G172:H172)</f>
-        <v/>
+      <c r="I172" s="9" t="n">
+        <v>4285.08</v>
       </c>
       <c r="J172" s="8" t="n">
         <v>8</v>
@@ -6321,9 +6161,8 @@
         <v>5533.86</v>
       </c>
       <c r="H173" s="9" t="n"/>
-      <c r="I173" s="9">
-        <f>SUM(G173:H173)</f>
-        <v/>
+      <c r="I173" s="9" t="n">
+        <v>5533.86</v>
       </c>
       <c r="J173" s="8" t="n">
         <v>25</v>
@@ -6356,9 +6195,8 @@
       <c r="H174" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I174" s="9">
-        <f>SUM(G174:H174)</f>
-        <v/>
+      <c r="I174" s="9" t="n">
+        <v>-122000</v>
       </c>
       <c r="J174" s="8" t="n">
         <v>10</v>
@@ -6391,9 +6229,8 @@
       <c r="H175" s="9" t="n">
         <v>3965</v>
       </c>
-      <c r="I175" s="9">
-        <f>SUM(G175:H175)</f>
-        <v/>
+      <c r="I175" s="9" t="n">
+        <v>19607.18</v>
       </c>
       <c r="J175" s="8" t="n">
         <v>98</v>
@@ -6426,9 +6263,8 @@
       <c r="H176" s="9" t="n">
         <v>29235.93</v>
       </c>
-      <c r="I176" s="9">
-        <f>SUM(G176:H176)</f>
-        <v/>
+      <c r="I176" s="9" t="n">
+        <v>-5426.190000000002</v>
       </c>
       <c r="J176" s="8" t="n">
         <v>45</v>
@@ -6461,9 +6297,8 @@
       <c r="H177" s="9" t="n">
         <v>46566.47</v>
       </c>
-      <c r="I177" s="9">
-        <f>SUM(G177:H177)</f>
-        <v/>
+      <c r="I177" s="9" t="n">
+        <v>-62218.64999999999</v>
       </c>
       <c r="J177" s="8" t="n">
         <v>103</v>
@@ -6494,9 +6329,8 @@
         <v>-14290.34</v>
       </c>
       <c r="H178" s="9" t="n"/>
-      <c r="I178" s="9">
-        <f>SUM(G178:H178)</f>
-        <v/>
+      <c r="I178" s="9" t="n">
+        <v>-14290.34</v>
       </c>
       <c r="J178" s="8" t="n">
         <v>2</v>
@@ -6529,9 +6363,8 @@
       <c r="H179" s="9" t="n">
         <v>8287.49</v>
       </c>
-      <c r="I179" s="9">
-        <f>SUM(G179:H179)</f>
-        <v/>
+      <c r="I179" s="9" t="n">
+        <v>-8332.059999999999</v>
       </c>
       <c r="J179" s="8" t="n">
         <v>19</v>
@@ -6562,9 +6395,8 @@
         <v>-1471.09</v>
       </c>
       <c r="H180" s="9" t="n"/>
-      <c r="I180" s="9">
-        <f>SUM(G180:H180)</f>
-        <v/>
+      <c r="I180" s="9" t="n">
+        <v>-1471.09</v>
       </c>
       <c r="J180" s="8" t="n">
         <v>32</v>
@@ -6597,9 +6429,8 @@
       <c r="H181" s="9" t="n">
         <v>25486.76</v>
       </c>
-      <c r="I181" s="9">
-        <f>SUM(G181:H181)</f>
-        <v/>
+      <c r="I181" s="9" t="n">
+        <v>5930.59</v>
       </c>
       <c r="J181" s="8" t="n">
         <v>62</v>
@@ -6632,9 +6463,8 @@
       <c r="H182" s="9" t="n">
         <v>132</v>
       </c>
-      <c r="I182" s="9">
-        <f>SUM(G182:H182)</f>
-        <v/>
+      <c r="I182" s="9" t="n">
+        <v>8847.889999999999</v>
       </c>
       <c r="J182" s="8" t="n">
         <v>9</v>
@@ -6667,9 +6497,8 @@
       <c r="H183" s="9" t="n">
         <v>7986.92</v>
       </c>
-      <c r="I183" s="9">
-        <f>SUM(G183:H183)</f>
-        <v/>
+      <c r="I183" s="9" t="n">
+        <v>-7966.16</v>
       </c>
       <c r="J183" s="8" t="n">
         <v>18</v>
@@ -6702,9 +6531,8 @@
       <c r="H184" s="9" t="n">
         <v>3115.41</v>
       </c>
-      <c r="I184" s="9">
-        <f>SUM(G184:H184)</f>
-        <v/>
+      <c r="I184" s="9" t="n">
+        <v>-1870.85</v>
       </c>
       <c r="J184" s="8" t="n">
         <v>16</v>
@@ -6737,9 +6565,8 @@
       <c r="H185" s="9" t="n">
         <v>3720</v>
       </c>
-      <c r="I185" s="9">
-        <f>SUM(G185:H185)</f>
-        <v/>
+      <c r="I185" s="9" t="n">
+        <v>4964.98</v>
       </c>
       <c r="J185" s="8" t="n">
         <v>8</v>
@@ -6772,9 +6599,8 @@
       <c r="H186" s="9" t="n">
         <v>45124.3</v>
       </c>
-      <c r="I186" s="9">
-        <f>SUM(G186:H186)</f>
-        <v/>
+      <c r="I186" s="9" t="n">
+        <v>-26844.78999999999</v>
       </c>
       <c r="J186" s="8" t="n">
         <v>102</v>
@@ -6805,9 +6631,8 @@
         <v>7000</v>
       </c>
       <c r="H187" s="9" t="n"/>
-      <c r="I187" s="9">
-        <f>SUM(G187:H187)</f>
-        <v/>
+      <c r="I187" s="9" t="n">
+        <v>7000</v>
       </c>
       <c r="J187" s="8" t="n">
         <v>3</v>
@@ -6840,9 +6665,8 @@
       <c r="H188" s="9" t="n">
         <v>5188.38</v>
       </c>
-      <c r="I188" s="9">
-        <f>SUM(G188:H188)</f>
-        <v/>
+      <c r="I188" s="9" t="n">
+        <v>5054.04</v>
       </c>
       <c r="J188" s="8" t="n">
         <v>24</v>
@@ -6875,9 +6699,8 @@
       <c r="H189" s="9" t="n">
         <v>9618.66</v>
       </c>
-      <c r="I189" s="9">
-        <f>SUM(G189:H189)</f>
-        <v/>
+      <c r="I189" s="9" t="n">
+        <v>-4766.389999999999</v>
       </c>
       <c r="J189" s="8" t="n">
         <v>31</v>
@@ -6910,9 +6733,8 @@
       <c r="H190" s="9" t="n">
         <v>22.69</v>
       </c>
-      <c r="I190" s="9">
-        <f>SUM(G190:H190)</f>
-        <v/>
+      <c r="I190" s="9" t="n">
+        <v>211.74</v>
       </c>
       <c r="J190" s="8" t="n">
         <v>4</v>
@@ -6945,9 +6767,8 @@
       <c r="H191" s="9" t="n">
         <v>11196.41</v>
       </c>
-      <c r="I191" s="9">
-        <f>SUM(G191:H191)</f>
-        <v/>
+      <c r="I191" s="9" t="n">
+        <v>-5616.360000000001</v>
       </c>
       <c r="J191" s="8" t="n">
         <v>57</v>
@@ -6980,9 +6801,8 @@
       <c r="H192" s="9" t="n">
         <v>3126.56</v>
       </c>
-      <c r="I192" s="9">
-        <f>SUM(G192:H192)</f>
-        <v/>
+      <c r="I192" s="9" t="n">
+        <v>-6053.6</v>
       </c>
       <c r="J192" s="8" t="n">
         <v>53</v>
@@ -7013,9 +6833,8 @@
         <v>4177.21</v>
       </c>
       <c r="H193" s="9" t="n"/>
-      <c r="I193" s="9">
-        <f>SUM(G193:H193)</f>
-        <v/>
+      <c r="I193" s="9" t="n">
+        <v>4177.21</v>
       </c>
       <c r="J193" s="8" t="n">
         <v>33</v>
@@ -7048,9 +6867,8 @@
       <c r="H194" s="9" t="n">
         <v>89355.84</v>
       </c>
-      <c r="I194" s="9">
-        <f>SUM(G194:H194)</f>
-        <v/>
+      <c r="I194" s="9" t="n">
+        <v>1057.690000000002</v>
       </c>
       <c r="J194" s="8" t="n">
         <v>100</v>
@@ -7083,9 +6901,8 @@
       <c r="H195" s="9" t="n">
         <v>5132.03</v>
       </c>
-      <c r="I195" s="9">
-        <f>SUM(G195:H195)</f>
-        <v/>
+      <c r="I195" s="9" t="n">
+        <v>-17387.53</v>
       </c>
       <c r="J195" s="8" t="n">
         <v>27</v>
@@ -7116,9 +6933,8 @@
         <v>7249.24</v>
       </c>
       <c r="H196" s="9" t="n"/>
-      <c r="I196" s="9">
-        <f>SUM(G196:H196)</f>
-        <v/>
+      <c r="I196" s="9" t="n">
+        <v>7249.24</v>
       </c>
       <c r="J196" s="8" t="n">
         <v>35</v>
@@ -7149,14 +6965,15 @@
         <v>266.97</v>
       </c>
       <c r="H197" s="9" t="n"/>
-      <c r="I197" s="9">
-        <f>SUM(G197:H197)</f>
-        <v/>
+      <c r="I197" s="9" t="n">
+        <v>266.97</v>
       </c>
       <c r="J197" s="8" t="n">
         <v>12</v>
       </c>
     </row>
+    <row r="198"/>
+    <row r="199"/>
     <row r="200">
       <c r="C200" t="inlineStr">
         <is>
